--- a/docentes/Flores Paz Victor - Estadisticos 20232.xlsx
+++ b/docentes/Flores Paz Victor - Estadisticos 20232.xlsx
@@ -649,16 +649,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -672,16 +675,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.83</v>
+      </c>
+      <c r="H3">
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -695,16 +701,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>86.67</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -718,16 +727,19 @@
         <v>31</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>31</v>
       </c>
-      <c r="E5">
-        <v>31</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -741,16 +753,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -806,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -858,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>90</v>
+        <v>86.67</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -893,7 +908,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -910,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Paz Victor - Estadisticos 20232.xlsx
+++ b/docentes/Flores Paz Victor - Estadisticos 20232.xlsx
@@ -821,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -856,7 +856,7 @@
         <v>95.83</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -873,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>86.67</v>
+        <v>76.67</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -908,7 +908,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -934,7 +934,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
